--- a/dde-webhook/assets/fqhc-sliding-fee-scale-template.xlsx
+++ b/dde-webhook/assets/fqhc-sliding-fee-scale-template.xlsx
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>400</v>
+        <v>25500</v>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="F21" s="12">
@@ -896,11 +896,11 @@
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>100</v>
+        <v>5200</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="F22" s="12">
